--- a/artfynd/A 58430-2024 artfynd.xlsx
+++ b/artfynd/A 58430-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121576161</v>
+        <v>121576173</v>
       </c>
       <c r="B2" t="n">
-        <v>57508</v>
+        <v>57372</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,33 +691,29 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -727,13 +723,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>582593</v>
+        <v>582614</v>
       </c>
       <c r="R2" t="n">
-        <v>6383936</v>
+        <v>6383885</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -763,6 +759,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-12-12</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Bearbetat stubbe</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -789,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121576173</v>
+        <v>121576161</v>
       </c>
       <c r="B3" t="n">
-        <v>57371</v>
+        <v>57509</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -805,29 +806,33 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -837,13 +842,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>582614</v>
+        <v>582593</v>
       </c>
       <c r="R3" t="n">
-        <v>6383885</v>
+        <v>6383936</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -873,11 +878,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-12-12</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Bearbetat stubbe</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 58430-2024 artfynd.xlsx
+++ b/artfynd/A 58430-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121576173</v>
+        <v>121576161</v>
       </c>
       <c r="B2" t="n">
-        <v>57372</v>
+        <v>57509</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,29 +691,33 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -723,13 +727,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>582614</v>
+        <v>582593</v>
       </c>
       <c r="R2" t="n">
-        <v>6383885</v>
+        <v>6383936</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -759,11 +763,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-12-12</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Bearbetat stubbe</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -790,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121576161</v>
+        <v>121576173</v>
       </c>
       <c r="B3" t="n">
-        <v>57509</v>
+        <v>57372</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -806,33 +805,29 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -842,13 +837,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>582593</v>
+        <v>582614</v>
       </c>
       <c r="R3" t="n">
-        <v>6383936</v>
+        <v>6383885</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -878,6 +873,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-12-12</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Bearbetat stubbe</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 58430-2024 artfynd.xlsx
+++ b/artfynd/A 58430-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121576161</v>
+        <v>121576173</v>
       </c>
       <c r="B2" t="n">
-        <v>57509</v>
+        <v>57372</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,33 +691,29 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -727,13 +723,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>582593</v>
+        <v>582614</v>
       </c>
       <c r="R2" t="n">
-        <v>6383936</v>
+        <v>6383885</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -763,6 +759,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-12-12</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Bearbetat stubbe</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -789,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121576173</v>
+        <v>121576161</v>
       </c>
       <c r="B3" t="n">
-        <v>57372</v>
+        <v>57509</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -805,29 +806,33 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -837,13 +842,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>582614</v>
+        <v>582593</v>
       </c>
       <c r="R3" t="n">
-        <v>6383885</v>
+        <v>6383936</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -873,11 +878,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-12-12</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Bearbetat stubbe</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 58430-2024 artfynd.xlsx
+++ b/artfynd/A 58430-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121576173</v>
+        <v>121576161</v>
       </c>
       <c r="B2" t="n">
-        <v>57372</v>
+        <v>57510</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,29 +691,33 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -723,13 +727,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>582614</v>
+        <v>582593</v>
       </c>
       <c r="R2" t="n">
-        <v>6383885</v>
+        <v>6383936</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -759,11 +763,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-12-12</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Bearbetat stubbe</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -790,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121576161</v>
+        <v>121576173</v>
       </c>
       <c r="B3" t="n">
-        <v>57509</v>
+        <v>57373</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -806,33 +805,29 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -842,13 +837,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>582593</v>
+        <v>582614</v>
       </c>
       <c r="R3" t="n">
-        <v>6383936</v>
+        <v>6383885</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -878,6 +873,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-12-12</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Bearbetat stubbe</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 58430-2024 artfynd.xlsx
+++ b/artfynd/A 58430-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121576173</v>
+        <v>121576161</v>
       </c>
       <c r="B2" t="n">
-        <v>57373</v>
+        <v>57510</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,29 +691,33 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -723,13 +727,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>582614</v>
+        <v>582593</v>
       </c>
       <c r="R2" t="n">
-        <v>6383885</v>
+        <v>6383936</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -759,11 +763,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-12-12</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Bearbetat stubbe</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -790,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121576161</v>
+        <v>121576173</v>
       </c>
       <c r="B3" t="n">
-        <v>57510</v>
+        <v>57373</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -806,33 +805,29 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -842,13 +837,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>582593</v>
+        <v>582614</v>
       </c>
       <c r="R3" t="n">
-        <v>6383936</v>
+        <v>6383885</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -878,6 +873,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-12-12</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Bearbetat stubbe</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 58430-2024 artfynd.xlsx
+++ b/artfynd/A 58430-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121576161</v>
+        <v>121576173</v>
       </c>
       <c r="B2" t="n">
-        <v>57510</v>
+        <v>57373</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,33 +691,29 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -727,13 +723,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>582593</v>
+        <v>582614</v>
       </c>
       <c r="R2" t="n">
-        <v>6383936</v>
+        <v>6383885</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -763,6 +759,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-12-12</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Bearbetat stubbe</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -789,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121576173</v>
+        <v>121576161</v>
       </c>
       <c r="B3" t="n">
-        <v>57373</v>
+        <v>57510</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -805,29 +806,33 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -837,13 +842,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>582614</v>
+        <v>582593</v>
       </c>
       <c r="R3" t="n">
-        <v>6383885</v>
+        <v>6383936</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -873,11 +878,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-12-12</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Bearbetat stubbe</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 58430-2024 artfynd.xlsx
+++ b/artfynd/A 58430-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121576161</v>
       </c>
       <c r="B2" t="n">
-        <v>57510</v>
+        <v>57518</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -792,7 +792,7 @@
         <v>121576173</v>
       </c>
       <c r="B3" t="n">
-        <v>57373</v>
+        <v>57381</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
